--- a/inventory.xlsx
+++ b/inventory.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3520" uniqueCount="1171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3520" uniqueCount="1172">
   <si>
     <t>2026</t>
   </si>
@@ -3504,9 +3504,6 @@
     <t>922075CL0</t>
   </si>
   <si>
-    <t>A035</t>
-  </si>
-  <si>
     <t>상추 엠-랩231</t>
   </si>
   <si>
@@ -3532,6 +3529,14 @@
   </si>
   <si>
     <t>922423CL0</t>
+  </si>
+  <si>
+    <t>A034</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>A034</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -13955,13 +13960,13 @@
     </row>
     <row r="720" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A720" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B720" s="2" t="s">
         <v>1161</v>
       </c>
-      <c r="B720" s="2" t="s">
+      <c r="C720" s="2" t="s">
         <v>1162</v>
-      </c>
-      <c r="C720" s="2" t="s">
-        <v>1163</v>
       </c>
       <c r="D720" s="2" t="s">
         <v>30</v>
@@ -14389,7 +14394,7 @@
     </row>
     <row r="751" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A751" s="2" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="B751" s="2" t="s">
         <v>417</v>
@@ -15375,7 +15380,7 @@
         <v>351</v>
       </c>
       <c r="C821" s="2" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="D821" s="2" t="s">
         <v>7</v>
@@ -15565,13 +15570,13 @@
     </row>
     <row r="835" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A835" s="2" t="s">
-        <v>1161</v>
+        <v>1171</v>
       </c>
       <c r="B835" s="2" t="s">
         <v>348</v>
       </c>
       <c r="C835" s="2" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="D835" s="2" t="s">
         <v>3</v>
@@ -15733,13 +15738,13 @@
     </row>
     <row r="847" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A847" s="2" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="B847" s="2" t="s">
         <v>385</v>
       </c>
       <c r="C847" s="2" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="D847" s="2" t="s">
         <v>10</v>
@@ -15761,13 +15766,13 @@
     </row>
     <row r="849" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A849" s="2" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="B849" s="2" t="s">
         <v>830</v>
       </c>
       <c r="C849" s="2" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="D849" s="2" t="s">
         <v>10</v>
